--- a/esyluban/examples/release/DataTables/l10n/texts.xlsx
+++ b/esyluban/examples/release/DataTables/l10n/texts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,6 +422,11 @@
           <t>##export</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>full_name="text.TbText" &amp; read_schema_from_file="true"</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -593,16 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
